--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_35.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1726317.817026575</v>
+        <v>1718310.975219677</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7069717.394383965</v>
+        <v>7069717.394383963</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7069717.394383965</v>
+        <v>7069717.394383963</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18755839.0331069</v>
+        <v>18755839.03310691</v>
       </c>
     </row>
   </sheetData>
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>124.8478761796818</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>352.6886318667089</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -900,7 +900,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>172.7782809922831</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>256.7073076836775</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
         <v>192.2818334606677</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>358.9068234179159</v>
+        <v>131.9860885083954</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1027,7 +1027,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>172.1723636724307</v>
       </c>
       <c r="H8" t="n">
-        <v>176.4246500889419</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>330.2103592575546</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1270,7 +1270,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>203.4946800714414</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1553,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>63.92422969792949</v>
+        <v>59.71994563975611</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>424.2212965486107</v>
+        <v>429.7144891057306</v>
       </c>
       <c r="V14" t="n">
         <v>404.8510241668239</v>
@@ -1857,10 +1857,10 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H17" t="n">
-        <v>188.5028512606473</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>298.1954887808113</v>
+        <v>345.9207354288559</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S20" t="n">
-        <v>269.8481678023229</v>
+        <v>275.3413603594427</v>
       </c>
       <c r="T20" t="n">
         <v>361.6755817285639</v>
@@ -2145,7 +2145,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>291.8106252399262</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>345.9207354288559</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>282.0825727406839</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2325,7 +2325,7 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>185.3828212651317</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G23" t="n">
         <v>178.7573722870162</v>
@@ -2364,7 +2364,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S23" t="n">
-        <v>269.8481678023229</v>
+        <v>275.3413603594427</v>
       </c>
       <c r="T23" t="n">
         <v>361.6755817285639</v>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>155.6780731376276</v>
+        <v>344.5479255901462</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>184.8564821639885</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
         <v>179.8896287080119</v>
@@ -2571,7 +2571,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -2720,13 +2720,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2.563877378261357</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>229.9677708001137</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
         <v>185.3391557398498</v>
@@ -2850,7 +2850,7 @@
         <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>413.3734759809475</v>
+        <v>418.8666685380672</v>
       </c>
       <c r="X29" t="n">
         <v>367.2818334606677</v>
@@ -2960,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>142.2291713307485</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>127.3292344295467</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>262.4925055126944</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C32" t="n">
         <v>224.4745782429939</v>
@@ -3045,7 +3045,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3227,10 +3227,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>344.5479255901462</v>
       </c>
       <c r="R34" t="n">
-        <v>280.0358089901587</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>97.2343191717691</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
@@ -3634,7 +3634,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
         <v>64.51066719152016</v>
@@ -3643,10 +3643,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="40">
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U42" t="n">
         <v>50.21035976018675</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="43">
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4057,7 +4057,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4069,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1220.129558715245</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="C3" t="n">
-        <v>1220.129558715245</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="D3" t="n">
-        <v>1094.020592877183</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="E3" t="n">
-        <v>747.8871613398975</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="F3" t="n">
-        <v>747.8871613398975</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>747.8871613398975</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="H3" t="n">
-        <v>747.8871613398975</v>
+        <v>33.68</v>
       </c>
       <c r="I3" t="n">
-        <v>528.5675796314646</v>
+        <v>33.68</v>
       </c>
       <c r="J3" t="n">
-        <v>652.5240998067635</v>
+        <v>157.636520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>841.7169159011469</v>
+        <v>346.8293362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>1113.067377496347</v>
+        <v>618.1797978648824</v>
       </c>
       <c r="M3" t="n">
-        <v>1199.147919239206</v>
+        <v>704.2603396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>1332.428203846775</v>
+        <v>837.54062421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1571.470655530493</v>
+        <v>1076.583075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>1684</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1509.172459504566</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.411048098122</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S3" t="n">
-        <v>1293.174684497505</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T3" t="n">
-        <v>1287.76280043941</v>
+        <v>792.8752208079458</v>
       </c>
       <c r="U3" t="n">
-        <v>1287.550315833161</v>
+        <v>436.6240775082397</v>
       </c>
       <c r="V3" t="n">
-        <v>1272.893076245767</v>
+        <v>421.9668379208456</v>
       </c>
       <c r="W3" t="n">
-        <v>1240.192931892404</v>
+        <v>389.2666935674835</v>
       </c>
       <c r="X3" t="n">
-        <v>1220.129558715245</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="Y3" t="n">
-        <v>1220.129558715245</v>
+        <v>369.2033203903244</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>600.7816666711694</v>
+        <v>724.5905067713542</v>
       </c>
       <c r="C4" t="n">
-        <v>600.7816666711694</v>
+        <v>724.5905067713542</v>
       </c>
       <c r="D4" t="n">
-        <v>714.1008107961695</v>
+        <v>837.9096508963543</v>
       </c>
       <c r="E4" t="n">
-        <v>831.9297150075826</v>
+        <v>837.9096508963543</v>
       </c>
       <c r="F4" t="n">
-        <v>956.290687599518</v>
+        <v>962.2706234882897</v>
       </c>
       <c r="G4" t="n">
-        <v>1109.697253486403</v>
+        <v>962.2706234882897</v>
       </c>
       <c r="H4" t="n">
-        <v>1212.989930203873</v>
+        <v>962.2706234882897</v>
       </c>
       <c r="I4" t="n">
-        <v>1434.122809139956</v>
+        <v>1183.403502424373</v>
       </c>
       <c r="J4" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T4" t="n">
-        <v>70.93025509417312</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>317.4814477324597</v>
+        <v>468.3068717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>317.4814477324597</v>
+        <v>468.3068717970915</v>
       </c>
       <c r="W4" t="n">
-        <v>489.3723659921371</v>
+        <v>613.1812060923219</v>
       </c>
       <c r="X4" t="n">
-        <v>489.3723659921371</v>
+        <v>613.1812060923219</v>
       </c>
       <c r="Y4" t="n">
-        <v>600.7816666711694</v>
+        <v>724.5905067713542</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266.9273161322752</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>216.9529946747056</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D5" t="n">
-        <v>206.5094030182917</v>
+        <v>225.028424940241</v>
       </c>
       <c r="E5" t="n">
-        <v>202.1020397790304</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>197.1630208820488</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G5" t="n">
-        <v>193.3676953396081</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H5" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I5" t="n">
         <v>33.68</v>
@@ -4597,13 +4597,13 @@
         <v>915.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>656.4208303737385</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>462.1967561710438</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>349.7549049762899</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4658,31 +4658,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1014.284879873102</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>865.523468466658</v>
+        <v>1040.351008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>798.2871048660405</v>
+        <v>973.1146453614743</v>
       </c>
       <c r="T6" t="n">
-        <v>792.8752208079458</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>792.6627362016965</v>
+        <v>563.4498726567263</v>
       </c>
       <c r="V6" t="n">
-        <v>778.0054966143024</v>
+        <v>548.7926330693322</v>
       </c>
       <c r="W6" t="n">
-        <v>745.3053522609403</v>
+        <v>516.09248871597</v>
       </c>
       <c r="X6" t="n">
-        <v>725.2419790837811</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="Y6" t="n">
-        <v>725.2419790837811</v>
+        <v>496.0291155388109</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>702.4333101621382</v>
+        <v>902.6378817599947</v>
       </c>
       <c r="C7" t="n">
-        <v>828.435315980574</v>
+        <v>927.7579214505071</v>
       </c>
       <c r="D7" t="n">
-        <v>941.7544601055741</v>
+        <v>927.7579214505071</v>
       </c>
       <c r="E7" t="n">
-        <v>1059.583364316987</v>
+        <v>1045.58682566192</v>
       </c>
       <c r="F7" t="n">
-        <v>1059.583364316987</v>
+        <v>1169.947798253856</v>
       </c>
       <c r="G7" t="n">
-        <v>1212.989930203873</v>
+        <v>1323.354364140741</v>
       </c>
       <c r="H7" t="n">
-        <v>1212.989930203873</v>
+        <v>1323.354364140741</v>
       </c>
       <c r="I7" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="J7" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K7" t="n">
         <v>1544.487243076824</v>
@@ -4743,25 +4743,25 @@
         <v>33.68</v>
       </c>
       <c r="S7" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T7" t="n">
-        <v>259.005934252978</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="U7" t="n">
-        <v>259.005934252978</v>
+        <v>468.3068717970915</v>
       </c>
       <c r="V7" t="n">
-        <v>268.1023001992351</v>
+        <v>468.3068717970915</v>
       </c>
       <c r="W7" t="n">
-        <v>439.9932184589125</v>
+        <v>640.1977900567689</v>
       </c>
       <c r="X7" t="n">
-        <v>591.0240094831059</v>
+        <v>791.2285810809624</v>
       </c>
       <c r="Y7" t="n">
-        <v>702.4333101621382</v>
+        <v>902.6378817599947</v>
       </c>
     </row>
     <row r="8">
@@ -4786,7 +4786,7 @@
         <v>215.6820428039981</v>
       </c>
       <c r="G8" t="n">
-        <v>211.8867172615575</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H8" t="n">
         <v>33.68</v>
@@ -4798,7 +4798,7 @@
         <v>33.68</v>
       </c>
       <c r="K8" t="n">
-        <v>450.47</v>
+        <v>33.68</v>
       </c>
       <c r="L8" t="n">
         <v>450.47</v>
@@ -4810,7 +4810,7 @@
         <v>1284.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1284.05</v>
+        <v>1684</v>
       </c>
       <c r="P8" t="n">
         <v>1684</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>369.2033203903244</v>
+        <v>367.2258174318733</v>
       </c>
       <c r="C9" t="n">
-        <v>369.2033203903244</v>
+        <v>367.2258174318733</v>
       </c>
       <c r="D9" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="E9" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="F9" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="G9" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="H9" t="n">
         <v>33.68</v>
@@ -4895,31 +4895,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S9" t="n">
-        <v>615.0984837095665</v>
+        <v>440.2709432141327</v>
       </c>
       <c r="T9" t="n">
-        <v>609.6865996514717</v>
+        <v>434.8590591560379</v>
       </c>
       <c r="U9" t="n">
-        <v>609.4741150452224</v>
+        <v>434.6465745497887</v>
       </c>
       <c r="V9" t="n">
-        <v>594.8168754578284</v>
+        <v>419.9893349623946</v>
       </c>
       <c r="W9" t="n">
-        <v>389.2666935674835</v>
+        <v>387.2891906090325</v>
       </c>
       <c r="X9" t="n">
-        <v>369.2033203903244</v>
+        <v>367.2258174318733</v>
       </c>
       <c r="Y9" t="n">
-        <v>369.2033203903244</v>
+        <v>367.2258174318733</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>667.1282646830375</v>
+        <v>420.7824390043126</v>
       </c>
       <c r="C10" t="n">
-        <v>667.1282646830375</v>
+        <v>420.7824390043126</v>
       </c>
       <c r="D10" t="n">
-        <v>780.4474088080376</v>
+        <v>534.1015831293126</v>
       </c>
       <c r="E10" t="n">
-        <v>780.4474088080376</v>
+        <v>534.1015831293126</v>
       </c>
       <c r="F10" t="n">
-        <v>780.4474088080376</v>
+        <v>658.4625557212481</v>
       </c>
       <c r="G10" t="n">
-        <v>851.9061895514213</v>
+        <v>811.8691216081334</v>
       </c>
       <c r="H10" t="n">
-        <v>851.9061895514213</v>
+        <v>981.3857067675309</v>
       </c>
       <c r="I10" t="n">
-        <v>1073.039068487504</v>
+        <v>1202.518585703614</v>
       </c>
       <c r="J10" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K10" t="n">
         <v>1544.487243076824</v>
@@ -4980,25 +4980,25 @@
         <v>33.68</v>
       </c>
       <c r="S10" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>221.7556791588049</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>468.3068717970915</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V10" t="n">
-        <v>667.1282646830375</v>
+        <v>269.7516479801191</v>
       </c>
       <c r="W10" t="n">
-        <v>667.1282646830375</v>
+        <v>269.7516479801191</v>
       </c>
       <c r="X10" t="n">
-        <v>667.1282646830375</v>
+        <v>420.7824390043126</v>
       </c>
       <c r="Y10" t="n">
-        <v>667.1282646830375</v>
+        <v>420.7824390043126</v>
       </c>
     </row>
     <row r="11">
@@ -5047,10 +5047,10 @@
         <v>3213.474122458845</v>
       </c>
       <c r="O11" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>4068</v>
@@ -5108,22 +5108,22 @@
         <v>81.36</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>847.8042142372474</v>
+        <v>695.3814443439232</v>
       </c>
       <c r="L12" t="n">
-        <v>1341.904675832448</v>
+        <v>1189.481905939123</v>
       </c>
       <c r="M12" t="n">
-        <v>1650.735217575307</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N12" t="n">
-        <v>2006.765502182875</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O12" t="n">
         <v>2316.13518397327</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101.6063362035657</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="C13" t="n">
-        <v>101.6063362035657</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="D13" t="n">
-        <v>101.6063362035657</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="E13" t="n">
-        <v>101.6063362035657</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="F13" t="n">
-        <v>101.6063362035657</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="G13" t="n">
+        <v>110.3289358651566</v>
+      </c>
+      <c r="H13" t="n">
+        <v>106.5197175806933</v>
+      </c>
+      <c r="I13" t="n">
+        <v>154.4025965167762</v>
+      </c>
+      <c r="J13" t="n">
+        <v>342.2363371692276</v>
+      </c>
+      <c r="K13" t="n">
+        <v>342.2363371692276</v>
+      </c>
+      <c r="L13" t="n">
+        <v>141.6831774138951</v>
+      </c>
+      <c r="M13" t="n">
+        <v>141.6831774138951</v>
+      </c>
+      <c r="N13" t="n">
         <v>81.36</v>
       </c>
-      <c r="H13" t="n">
+      <c r="O13" t="n">
         <v>81.36</v>
       </c>
-      <c r="I13" t="n">
-        <v>129.2428789360829</v>
-      </c>
-      <c r="J13" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="K13" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="L13" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="M13" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="N13" t="n">
-        <v>252.5066906007267</v>
-      </c>
-      <c r="O13" t="n">
-        <v>252.5066906007267</v>
-      </c>
       <c r="P13" t="n">
-        <v>252.5066906007267</v>
+        <v>81.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>252.5066906007267</v>
+        <v>81.36</v>
       </c>
       <c r="R13" t="n">
-        <v>252.5066906007267</v>
+        <v>81.36</v>
       </c>
       <c r="S13" t="n">
-        <v>113.7455999917818</v>
+        <v>81.36</v>
       </c>
       <c r="T13" t="n">
-        <v>128.5712791505866</v>
+        <v>96.18567915880486</v>
       </c>
       <c r="U13" t="n">
-        <v>201.8724717888733</v>
+        <v>169.4868717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>227.4438646748193</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>227.4438646748193</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X13" t="n">
-        <v>227.4438646748193</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y13" t="n">
-        <v>164.3475486652613</v>
+        <v>130.5752720687223</v>
       </c>
     </row>
     <row r="14">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C14" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D14" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E14" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F14" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G14" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H14" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I14" t="n">
         <v>81.36</v>
@@ -5272,19 +5272,19 @@
         <v>81.36</v>
       </c>
       <c r="K14" t="n">
-        <v>791.0663663478683</v>
+        <v>736.7142979669047</v>
       </c>
       <c r="L14" t="n">
-        <v>1552.289212421678</v>
+        <v>1643.743792536527</v>
       </c>
       <c r="M14" t="n">
-        <v>2063.138041150613</v>
+        <v>2154.592621265462</v>
       </c>
       <c r="N14" t="n">
-        <v>2676.358360925376</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="O14" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P14" t="n">
         <v>3629.400904947332</v>
@@ -5302,19 +5302,19 @@
         <v>3403.957223879615</v>
       </c>
       <c r="U14" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V14" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W14" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X14" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y14" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>81.36</v>
       </c>
       <c r="I15" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>428.066520175299</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>840.0093362696824</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L15" t="n">
-        <v>1334.109797864882</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M15" t="n">
-        <v>1642.940339607742</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N15" t="n">
-        <v>1854.342732289551</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O15" t="n">
-        <v>2316.13518397327</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P15" t="n">
-        <v>2651.414528442776</v>
+        <v>2600.013000882351</v>
       </c>
       <c r="Q15" t="n">
         <v>2651.414528442776</v>
@@ -5500,7 +5500,7 @@
         <v>271.7669204653003</v>
       </c>
       <c r="H17" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I17" t="n">
         <v>81.36</v>
@@ -5509,10 +5509,10 @@
         <v>81.36</v>
       </c>
       <c r="K17" t="n">
-        <v>396.8920737197113</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L17" t="n">
-        <v>1303.921568289334</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M17" t="n">
         <v>1814.770397018269</v>
@@ -5588,10 +5588,10 @@
         <v>428.066520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>643.9799167834981</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>1138.080378378698</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M18" t="n">
         <v>1446.910920121557</v>
@@ -5643,49 +5643,49 @@
         <v>195.0582646830375</v>
       </c>
       <c r="C19" t="n">
-        <v>146.8509448365277</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D19" t="n">
-        <v>146.8509448365277</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E19" t="n">
-        <v>146.8509448365277</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F19" t="n">
-        <v>146.8509448365277</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="G19" t="n">
-        <v>146.8509448365277</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="H19" t="n">
-        <v>146.8509448365277</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="I19" t="n">
-        <v>194.7338237726106</v>
+        <v>242.9411436191204</v>
       </c>
       <c r="J19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="K19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="L19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="M19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="N19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="O19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="P19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="Q19" t="n">
-        <v>382.5675644250619</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="R19" t="n">
         <v>81.36</v>
@@ -5743,22 +5743,22 @@
         <v>81.36</v>
       </c>
       <c r="J20" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K20" t="n">
-        <v>690.7012485145707</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L20" t="n">
-        <v>690.7012485145707</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M20" t="n">
-        <v>1201.550077243506</v>
+        <v>2208.944689646426</v>
       </c>
       <c r="N20" t="n">
-        <v>1814.770397018269</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="O20" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P20" t="n">
         <v>3629.400904947332</v>
@@ -5770,22 +5770,22 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S20" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T20" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U20" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W20" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X20" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y20" t="n">
         <v>1483.211511357417</v>
@@ -5819,19 +5819,19 @@
         <v>81.36</v>
       </c>
       <c r="I21" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J21" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>847.8042142372474</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L21" t="n">
-        <v>1341.904675832448</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M21" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N21" t="n">
         <v>1802.941204729126</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="G22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="H22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="I22" t="n">
-        <v>178.4581510048052</v>
+        <v>242.9411436191204</v>
       </c>
       <c r="J22" t="n">
-        <v>366.2918916572565</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="K22" t="n">
-        <v>366.2918916572565</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="L22" t="n">
-        <v>366.2918916572565</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="M22" t="n">
-        <v>366.2918916572565</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="N22" t="n">
-        <v>366.2918916572565</v>
+        <v>81.36</v>
       </c>
       <c r="O22" t="n">
-        <v>366.2918916572565</v>
+        <v>81.36</v>
       </c>
       <c r="P22" t="n">
-        <v>366.2918916572565</v>
+        <v>81.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>366.2918916572565</v>
+        <v>81.36</v>
       </c>
       <c r="R22" t="n">
         <v>81.36</v>
@@ -5940,13 +5940,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y22" t="n">
-        <v>130.5752720687223</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="23">
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C23" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D23" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E23" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F23" t="n">
         <v>446.7812434247916</v>
@@ -5980,25 +5980,25 @@
         <v>81.36</v>
       </c>
       <c r="J23" t="n">
-        <v>419.5939772193697</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1129.300343567238</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1129.300343567238</v>
+        <v>1379.698607607278</v>
       </c>
       <c r="M23" t="n">
-        <v>1640.149172296173</v>
+        <v>1890.547436336213</v>
       </c>
       <c r="N23" t="n">
-        <v>2253.369492070936</v>
+        <v>2503.767756110976</v>
       </c>
       <c r="O23" t="n">
-        <v>3206.412036092893</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P23" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>4068</v>
@@ -6007,25 +6007,25 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S23" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T23" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U23" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W23" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X23" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y23" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="24">
@@ -6059,16 +6059,16 @@
         <v>81.36</v>
       </c>
       <c r="J24" t="n">
-        <v>232.0371006891147</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>643.9799167834981</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>1138.080378378698</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M24" t="n">
-        <v>1446.910920121557</v>
+        <v>1642.940339607742</v>
       </c>
       <c r="N24" t="n">
         <v>1802.941204729126</v>
@@ -6117,52 +6117,52 @@
         <v>193.6715880782802</v>
       </c>
       <c r="C25" t="n">
-        <v>145.4642682317704</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D25" t="n">
-        <v>145.4642682317704</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E25" t="n">
-        <v>145.4642682317704</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F25" t="n">
-        <v>145.4642682317704</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G25" t="n">
-        <v>145.4642682317704</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H25" t="n">
-        <v>141.6550499473072</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="I25" t="n">
-        <v>189.5379288833901</v>
+        <v>241.5544670143631</v>
       </c>
       <c r="J25" t="n">
-        <v>377.3716695358414</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="K25" t="n">
-        <v>377.3716695358414</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="L25" t="n">
-        <v>377.3716695358414</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="M25" t="n">
-        <v>377.3716695358414</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="N25" t="n">
-        <v>377.3716695358414</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="O25" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="P25" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="R25" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="S25" t="n">
         <v>81.36</v>
@@ -6202,37 +6202,37 @@
         <v>815.2116584470142</v>
       </c>
       <c r="E26" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F26" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G26" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H26" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I26" t="n">
         <v>81.36</v>
       </c>
       <c r="J26" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K26" t="n">
-        <v>472.6691130376557</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L26" t="n">
-        <v>1379.698607607278</v>
+        <v>1552.289212421678</v>
       </c>
       <c r="M26" t="n">
-        <v>1814.770397018269</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N26" t="n">
-        <v>1814.770397018269</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O26" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>3629.400904947332</v>
@@ -6354,46 +6354,46 @@
         <v>195.0582646830375</v>
       </c>
       <c r="C28" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="D28" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="E28" t="n">
-        <v>195.0582646830375</v>
+        <v>146.8509448365277</v>
       </c>
       <c r="F28" t="n">
-        <v>195.0582646830375</v>
+        <v>144.2611697069707</v>
       </c>
       <c r="G28" t="n">
-        <v>195.0582646830375</v>
+        <v>144.2611697069707</v>
       </c>
       <c r="H28" t="n">
-        <v>191.2490463985742</v>
+        <v>144.2611697069707</v>
       </c>
       <c r="I28" t="n">
-        <v>239.1319253346571</v>
+        <v>192.1440486430537</v>
       </c>
       <c r="J28" t="n">
-        <v>426.9656659871084</v>
+        <v>379.977789295505</v>
       </c>
       <c r="K28" t="n">
-        <v>426.9656659871084</v>
+        <v>379.977789295505</v>
       </c>
       <c r="L28" t="n">
-        <v>426.9656659871084</v>
+        <v>379.977789295505</v>
       </c>
       <c r="M28" t="n">
-        <v>426.9656659871084</v>
+        <v>81.36</v>
       </c>
       <c r="N28" t="n">
-        <v>426.9656659871084</v>
+        <v>81.36</v>
       </c>
       <c r="O28" t="n">
-        <v>426.9656659871084</v>
+        <v>81.36</v>
       </c>
       <c r="P28" t="n">
-        <v>426.9656659871084</v>
+        <v>81.36</v>
       </c>
       <c r="Q28" t="n">
         <v>81.36</v>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C29" t="n">
         <v>996.8742475204788</v>
@@ -6460,19 +6460,19 @@
         <v>1182.375479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>1182.375479385524</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M29" t="n">
-        <v>1693.224308114459</v>
+        <v>2593.19171631813</v>
       </c>
       <c r="N29" t="n">
-        <v>1814.770397018269</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="O29" t="n">
-        <v>2767.812941040225</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P29" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q29" t="n">
         <v>4068</v>
@@ -6493,13 +6493,13 @@
         <v>2566.510435278165</v>
       </c>
       <c r="W29" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X29" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y29" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="30">
@@ -6530,19 +6530,19 @@
         <v>81.36</v>
       </c>
       <c r="I30" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>428.066520175299</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>840.0093362696824</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L30" t="n">
-        <v>1334.109797864882</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M30" t="n">
-        <v>1642.940339607742</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N30" t="n">
         <v>1802.941204729126</v>
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G31" t="n">
-        <v>174.8119284794718</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H31" t="n">
-        <v>174.8119284794718</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I31" t="n">
-        <v>222.6948074155547</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J31" t="n">
-        <v>410.528548068006</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K31" t="n">
-        <v>410.528548068006</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L31" t="n">
-        <v>209.9753883126735</v>
+        <v>225.0258296270187</v>
       </c>
       <c r="M31" t="n">
-        <v>209.9753883126735</v>
+        <v>225.0258296270187</v>
       </c>
       <c r="N31" t="n">
-        <v>209.9753883126735</v>
+        <v>81.36</v>
       </c>
       <c r="O31" t="n">
-        <v>209.9753883126735</v>
+        <v>81.36</v>
       </c>
       <c r="P31" t="n">
-        <v>209.9753883126735</v>
+        <v>81.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>209.9753883126735</v>
+        <v>81.36</v>
       </c>
       <c r="R31" t="n">
         <v>81.36</v>
@@ -6651,13 +6651,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="32">
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C32" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D32" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E32" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F32" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G32" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H32" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I32" t="n">
         <v>81.36</v>
       </c>
       <c r="J32" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>791.0663663478683</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>1698.095860917491</v>
+        <v>1379.698607607278</v>
       </c>
       <c r="M32" t="n">
-        <v>1698.095860917491</v>
+        <v>1379.698607607278</v>
       </c>
       <c r="N32" t="n">
-        <v>2311.316180692254</v>
+        <v>1992.918927382041</v>
       </c>
       <c r="O32" t="n">
-        <v>3264.35872471421</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P32" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>4068</v>
@@ -6773,19 +6773,19 @@
         <v>428.066520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>840.0093362696824</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L33" t="n">
-        <v>1334.109797864882</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1642.940339607742</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>1998.97062421531</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>2460.763075899029</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P33" t="n">
         <v>2600.013000882351</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>132.3170522213418</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C34" t="n">
-        <v>132.3170522213418</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D34" t="n">
-        <v>132.3170522213418</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E34" t="n">
-        <v>132.3170522213418</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F34" t="n">
-        <v>132.3170522213418</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G34" t="n">
-        <v>132.3170522213418</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H34" t="n">
-        <v>128.5078339368786</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="I34" t="n">
-        <v>176.3907128729615</v>
+        <v>241.5544670143631</v>
       </c>
       <c r="J34" t="n">
-        <v>364.2244535254129</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="K34" t="n">
-        <v>364.2244535254129</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="L34" t="n">
-        <v>364.2244535254129</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="M34" t="n">
-        <v>364.2244535254129</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="N34" t="n">
-        <v>364.2244535254129</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="O34" t="n">
-        <v>364.2244535254129</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="P34" t="n">
-        <v>364.2244535254129</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="Q34" t="n">
-        <v>364.2244535254129</v>
+        <v>81.36</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6888,13 +6888,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="35">
@@ -6931,22 +6931,22 @@
         <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>64.92117127106526</v>
+        <v>598.13</v>
       </c>
       <c r="L35" t="n">
-        <v>618.3311712710653</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M35" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N35" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C36" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
         <v>44.72</v>
@@ -7040,7 +7040,7 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
         <v>357.8124310491301</v>
@@ -7049,10 +7049,10 @@
         <v>274.6072361907175</v>
       </c>
       <c r="X36" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y36" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
         <v>1010.366979583462</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7171,16 +7171,16 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M38" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N38" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="P38" t="n">
         <v>1797.400904947332</v>
@@ -7277,19 +7277,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>274.6072361907175</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
         <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7353,19 +7353,19 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
         <v>807.7884919737335</v>
@@ -7411,16 +7411,16 @@
         <v>598.13</v>
       </c>
       <c r="M41" t="n">
-        <v>1108.978828728935</v>
+        <v>598.13</v>
       </c>
       <c r="N41" t="n">
-        <v>1662.388828728935</v>
+        <v>1151.54</v>
       </c>
       <c r="O41" t="n">
-        <v>1662.388828728935</v>
+        <v>1682.59</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7505,25 +7505,25 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>763.9167385504073</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U42" t="n">
-        <v>713.1992034391076</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V42" t="n">
-        <v>648.0369133466629</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X42" t="n">
-        <v>494.2632948060407</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y42" t="n">
         <v>90.8376455473191</v>
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L44" t="n">
-        <v>598.13</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M44" t="n">
-        <v>598.13</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1151.54</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O44" t="n">
-        <v>1704.95</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="46">
@@ -8441,10 +8441,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>421</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>965.2621276423173</v>
@@ -8453,10 +8453,10 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>474.2377685639915</v>
       </c>
       <c r="P8" t="n">
-        <v>404.2769590305805</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
         <v>172.8226843274854</v>
@@ -8690,13 +8690,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>933.4053216358654</v>
+        <v>490.3759326937771</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,10 +8915,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>661.9740383504088</v>
       </c>
       <c r="L14" t="n">
-        <v>768.9119657311207</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,10 +8927,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9152,13 +9152,13 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>318.7192663835468</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>662.1151944107801</v>
       </c>
       <c r="N17" t="n">
         <v>477.2489580698352</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>220.2344802797121</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,10 +9401,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>1032.917105959907</v>
+        <v>885.6376630348439</v>
       </c>
       <c r="P20" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>376.6934882848577</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,13 +9638,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>1032.917105959907</v>
+        <v>336.9601775834349</v>
       </c>
       <c r="P23" t="n">
         <v>870.5779326741233</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>768.9119657311207</v>
       </c>
       <c r="M26" t="n">
-        <v>983.728581592813</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
         <v>1032.917105959907</v>
       </c>
       <c r="P26" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10103,22 +10103,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>1053.137624978664</v>
       </c>
       <c r="N29" t="n">
-        <v>600.0227852454004</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
         <v>870.5779326741233</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>916.1914086561842</v>
@@ -10349,13 +10349,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>1032.917105959907</v>
+        <v>852.9690954914502</v>
       </c>
       <c r="P32" t="n">
-        <v>812.0459239657215</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,10 +10574,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>20.40522350612653</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,13 +10586,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10814,19 +10814,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>801.385149773304</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>257.410082171668</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11054,19 +11054,19 @@
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>606.6620109882341</v>
       </c>
       <c r="P41" t="n">
-        <v>136.6628946047192</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
+        <v>257.1230221309868</v>
+      </c>
+      <c r="L44" t="n">
         <v>559</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>536.7012014548231</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23381,7 +23381,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
         <v>47.72524664804467</v>
@@ -23399,7 +23399,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23411,13 +23411,13 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>295.6316114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>282.2608455737554</v>
+        <v>286.4651296319288</v>
       </c>
       <c r="O13" t="n">
         <v>415.445564079015</v>
@@ -23432,7 +23432,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
@@ -23858,7 +23858,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D19" t="n">
         <v>60.53621805555548</v>
@@ -23903,7 +23903,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>203.4066392003398</v>
+        <v>155.6813925522951</v>
       </c>
       <c r="S19" t="n">
         <v>137.3734797028554</v>
@@ -24128,7 +24128,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>346.1850752716849</v>
+        <v>0.2643398428289743</v>
       </c>
       <c r="O22" t="n">
         <v>415.445564079015</v>
@@ -24140,7 +24140,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>219.5195552404671</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>137.3734797028554</v>
@@ -24155,13 +24155,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X22" t="n">
         <v>22.44364543010755</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -24332,7 +24332,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D25" t="n">
         <v>60.53621805555548</v>
@@ -24347,7 +24347,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -24368,7 +24368,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>259.7674909413874</v>
+        <v>70.89763848886872</v>
       </c>
       <c r="P25" t="n">
         <v>462.4478973282775</v>
@@ -24380,7 +24380,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24569,7 +24569,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>60.53621805555548</v>
@@ -24578,13 +24578,13 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>46.81897858948057</v>
       </c>
       <c r="G28" t="n">
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>346.1850752716849</v>
@@ -24611,7 +24611,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>158.6896570983607</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
@@ -24818,10 +24818,10 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24839,7 +24839,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>346.1850752716849</v>
+        <v>203.9559039409364</v>
       </c>
       <c r="O31" t="n">
         <v>415.445564079015</v>
@@ -24851,7 +24851,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>374.2728935516043</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25040,7 +25040,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C34" t="n">
         <v>47.72524664804467</v>
@@ -25058,7 +25058,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25085,10 +25085,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>500.839266425598</v>
+        <v>156.2913408354518</v>
       </c>
       <c r="R34" t="n">
-        <v>221.5663189909923</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>22.44364543010755</v>
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7549974.98265816</v>
+        <v>7549974.982658161</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8589738.213994989</v>
+        <v>8589738.213994991</v>
       </c>
     </row>
     <row r="10">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10669264.67666864</v>
+        <v>10669264.67666865</v>
       </c>
     </row>
     <row r="12">
@@ -26281,19 +26281,19 @@
         <v>1039763.231336832</v>
       </c>
       <c r="F2" t="n">
+        <v>1039763.231336833</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1039763.231336833</v>
+      </c>
+      <c r="H2" t="n">
         <v>1039763.231336832</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1039763.231336832</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1039763.231336833</v>
       </c>
       <c r="I2" t="n">
         <v>1039763.231336832</v>
       </c>
       <c r="J2" t="n">
-        <v>1039763.231336833</v>
+        <v>1039763.231336832</v>
       </c>
       <c r="K2" t="n">
         <v>1039763.231336833</v>
@@ -26308,7 +26308,7 @@
         <v>1101954.910291021</v>
       </c>
       <c r="O2" t="n">
-        <v>1101954.91029102</v>
+        <v>1101954.910291021</v>
       </c>
       <c r="P2" t="n">
         <v>1101954.910291021</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724099</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743712</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482318</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.290050781</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121192</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696402</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464519</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>328183.5510485113</v>
+        <v>326620.9379550662</v>
       </c>
       <c r="C6" t="n">
-        <v>478408.0668120558</v>
+        <v>476845.4537186106</v>
       </c>
       <c r="D6" t="n">
-        <v>480443.3398100947</v>
+        <v>478880.7267166497</v>
       </c>
       <c r="E6" t="n">
-        <v>123369.4168249707</v>
+        <v>121032.7089132729</v>
       </c>
       <c r="F6" t="n">
-        <v>514614.9675886005</v>
+        <v>512278.2596769033</v>
       </c>
       <c r="G6" t="n">
-        <v>516070.524197749</v>
+        <v>513733.8162860514</v>
       </c>
       <c r="H6" t="n">
-        <v>517528.101036411</v>
+        <v>515191.3931247132</v>
       </c>
       <c r="I6" t="n">
-        <v>518987.7126759973</v>
+        <v>516651.0047642996</v>
       </c>
       <c r="J6" t="n">
-        <v>192257.3738788901</v>
+        <v>189920.6659671922</v>
       </c>
       <c r="K6" t="n">
-        <v>521913.0996020783</v>
+        <v>519576.3916903808</v>
       </c>
       <c r="L6" t="n">
-        <v>523378.9050008955</v>
+        <v>521042.1970891978</v>
       </c>
       <c r="M6" t="n">
-        <v>362492.8357489198</v>
+        <v>360750.9859358121</v>
       </c>
       <c r="N6" t="n">
-        <v>513033.7327837732</v>
+        <v>511291.8829706657</v>
       </c>
       <c r="O6" t="n">
-        <v>335001.4720415112</v>
+        <v>333259.6222284037</v>
       </c>
       <c r="P6" t="n">
-        <v>516972.0748925216</v>
+        <v>515230.2250794142</v>
       </c>
     </row>
   </sheetData>
@@ -27518,10 +27518,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>223.0898107180208</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27530,10 +27530,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>47.52172789347776</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27600,25 +27600,25 @@
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
-        <v>333.1071631899714</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
         <v>400</v>
-      </c>
-      <c r="T4" t="n">
-        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27654,7 +27654,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>372.7105212480333</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
@@ -27679,7 +27679,7 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27733,7 +27733,7 @@
         <v>400</v>
       </c>
       <c r="W5" t="n">
-        <v>381.66616829727</v>
+        <v>400</v>
       </c>
       <c r="X5" t="n">
         <v>400</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.64973322841075</v>
+        <v>252.5704681379312</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27831,16 +27831,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>298.0990241132087</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27855,7 +27855,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,16 +27879,16 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>208.3585586467789</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
@@ -27922,10 +27922,10 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
+        <v>231.5850086145855</v>
+      </c>
+      <c r="H8" t="n">
         <v>400</v>
-      </c>
-      <c r="H8" t="n">
-        <v>231.5850086145855</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -27992,7 +27992,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>17.72732764014802</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28004,7 +28004,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28049,7 +28049,7 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>228.8784628383871</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28077,22 +28077,22 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>317.2244594510086</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>380.6918350714736</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28131,7 +28131,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28244,13 +28244,13 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>78.91122027701095</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28262,7 +28262,7 @@
         <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>71.03760616835936</v>
+        <v>225</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
@@ -28402,7 +28402,7 @@
         <v>225</v>
       </c>
       <c r="I14" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28438,7 +28438,7 @@
         <v>225</v>
       </c>
       <c r="U14" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="V14" t="n">
         <v>225</v>
@@ -28481,13 +28481,13 @@
         <v>225</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J15" t="n">
         <v>225</v>
       </c>
       <c r="K15" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="L15" t="n">
         <v>225</v>
@@ -28496,7 +28496,7 @@
         <v>225</v>
       </c>
       <c r="N15" t="n">
-        <v>78.9112202770111</v>
+        <v>225</v>
       </c>
       <c r="O15" t="n">
         <v>225</v>
@@ -28505,7 +28505,7 @@
         <v>225</v>
       </c>
       <c r="Q15" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R15" t="n">
         <v>225</v>
@@ -28636,10 +28636,10 @@
         <v>225</v>
       </c>
       <c r="H17" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28724,13 +28724,13 @@
         <v>225</v>
       </c>
       <c r="K18" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="L18" t="n">
         <v>225</v>
       </c>
       <c r="M18" t="n">
-        <v>225</v>
+        <v>26.99048536749062</v>
       </c>
       <c r="N18" t="n">
         <v>225</v>
@@ -28906,7 +28906,7 @@
         <v>225</v>
       </c>
       <c r="S20" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="T20" t="n">
         <v>225</v>
@@ -28924,7 +28924,7 @@
         <v>225</v>
       </c>
       <c r="Y20" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21">
@@ -28955,7 +28955,7 @@
         <v>225</v>
       </c>
       <c r="I21" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>225</v>
@@ -28967,10 +28967,10 @@
         <v>225</v>
       </c>
       <c r="M21" t="n">
-        <v>225</v>
+        <v>26.99048536749062</v>
       </c>
       <c r="N21" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O21" t="n">
         <v>225</v>
@@ -29104,7 +29104,7 @@
         <v>225</v>
       </c>
       <c r="F23" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="G23" t="n">
         <v>225</v>
@@ -29143,7 +29143,7 @@
         <v>225</v>
       </c>
       <c r="S23" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="T23" t="n">
         <v>225</v>
@@ -29195,7 +29195,7 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="K24" t="n">
         <v>225</v>
@@ -29207,7 +29207,7 @@
         <v>225</v>
       </c>
       <c r="N24" t="n">
-        <v>225</v>
+        <v>26.99048536749072</v>
       </c>
       <c r="O24" t="n">
         <v>225</v>
@@ -29338,7 +29338,7 @@
         <v>225</v>
       </c>
       <c r="E26" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="F26" t="n">
         <v>225</v>
@@ -29350,7 +29350,7 @@
         <v>225</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29569,7 +29569,7 @@
         <v>225</v>
       </c>
       <c r="C29" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="D29" t="n">
         <v>225</v>
@@ -29629,7 +29629,7 @@
         <v>225</v>
       </c>
       <c r="W29" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="X29" t="n">
         <v>225</v>
@@ -29666,7 +29666,7 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J30" t="n">
         <v>225</v>
@@ -29675,13 +29675,13 @@
         <v>225</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M30" t="n">
         <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>26.99048536749072</v>
+        <v>225</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="C32" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>225</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
         <v>225</v>
       </c>
       <c r="K33" t="n">
-        <v>225</v>
+        <v>26.99048536749061</v>
       </c>
       <c r="L33" t="n">
         <v>225</v>
@@ -29924,7 +29924,7 @@
         <v>225</v>
       </c>
       <c r="P33" t="n">
-        <v>26.99048536749045</v>
+        <v>225</v>
       </c>
       <c r="Q33" t="n">
         <v>225</v>
@@ -30131,7 +30131,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>276.9584798124344</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.7395358750273</v>
@@ -30176,16 +30176,16 @@
         <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30204,7 +30204,7 @@
         <v>350</v>
       </c>
       <c r="D37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="E37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
@@ -30413,7 +30413,7 @@
         <v>350</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -30422,10 +30422,10 @@
         <v>350</v>
       </c>
       <c r="X39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="40">
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30504,7 +30504,7 @@
         <v>350</v>
       </c>
       <c r="Y40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41">
@@ -30641,13 +30641,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
       </c>
       <c r="T42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>350</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>287.3222374745576</v>
       </c>
     </row>
     <row r="43">
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30836,7 +30836,7 @@
         <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722602</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -30848,10 +30848,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,7 +30878,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -34886,25 +34886,25 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>104.3360370883528</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34940,7 +34940,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>146.3377114093236</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -35117,16 +35117,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>25.37377746516403</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,16 +35165,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>9.188248430562721</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
@@ -35220,10 +35220,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>421</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>421</v>
@@ -35232,10 +35232,10 @@
         <v>421</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>403.989898989899</v>
       </c>
       <c r="P8" t="n">
-        <v>403.989898989899</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35363,22 +35363,22 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>72.18058660947851</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>345.4228862355658</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35417,7 +35417,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35469,13 +35469,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>863.157452061773</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,13 +35530,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>270.0150749178023</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35548,7 +35548,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>312.4946280711058</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
@@ -35694,10 +35694,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>661.9740383504088</v>
       </c>
       <c r="L14" t="n">
-        <v>768.9119657311207</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,10 +35706,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35767,13 +35767,13 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J15" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996305</v>
       </c>
       <c r="L15" t="n">
         <v>499.091375348687</v>
@@ -35782,7 +35782,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>213.5377703856659</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O15" t="n">
         <v>466.4570219027464</v>
@@ -35791,7 +35791,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,13 +35931,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>318.7192663835468</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>117.8530667684628</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -36010,13 +36010,13 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>218.0943400082819</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>499.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>311.9500421645043</v>
+        <v>113.9405275319949</v>
       </c>
       <c r="N18" t="n">
         <v>359.6265501086548</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>220.2344802797121</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,10 +36180,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>962.6692363858147</v>
+        <v>815.3897934607513</v>
       </c>
       <c r="P20" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36241,7 +36241,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>350.2086062376757</v>
@@ -36253,10 +36253,10 @@
         <v>499.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>311.9500421645043</v>
+        <v>113.9405275319949</v>
       </c>
       <c r="N21" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O21" t="n">
         <v>466.4570219027464</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>341.6504820397674</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,13 +36417,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>962.6692363858147</v>
+        <v>266.7123080093424</v>
       </c>
       <c r="P23" t="n">
         <v>870.2908726334418</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36481,7 +36481,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>152.1990916051663</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K24" t="n">
         <v>416.1038546407913</v>
@@ -36493,7 +36493,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>359.6265501086548</v>
+        <v>161.6170354761456</v>
       </c>
       <c r="O24" t="n">
         <v>466.4570219027464</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>768.9119657311207</v>
       </c>
       <c r="M26" t="n">
-        <v>439.4664539504957</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
         <v>962.6692363858147</v>
       </c>
       <c r="P26" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36882,22 +36882,22 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>508.8754973363467</v>
       </c>
       <c r="N29" t="n">
-        <v>122.7738271755652</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>870.2908726334418</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
         <v>350.2086062376757</v>
@@ -36961,13 +36961,13 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M30" t="n">
         <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>161.6170354761456</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>916.1914086561842</v>
@@ -37128,13 +37128,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>962.6692363858147</v>
+        <v>782.7212259173577</v>
       </c>
       <c r="P32" t="n">
-        <v>811.7588639250399</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37195,7 +37195,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>416.1038546407913</v>
+        <v>218.0943400082819</v>
       </c>
       <c r="L33" t="n">
         <v>499.091375348687</v>
@@ -37210,7 +37210,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>140.6564898821437</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>51.92073490952041</v>
@@ -37353,10 +37353,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>20.40522350612653</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
@@ -37365,13 +37365,13 @@
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37490,7 +37490,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E37" t="n">
         <v>69.01909516304346</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37593,19 +37593,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>257.1230221309867</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37790,7 +37790,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>54.74597778467183</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37833,19 +37833,19 @@
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>536.4141414141416</v>
       </c>
       <c r="P41" t="n">
-        <v>136.3758345640378</v>
+        <v>559</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
+        <v>257.1230221309868</v>
+      </c>
+      <c r="L44" t="n">
         <v>559</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>559</v>
       </c>
-      <c r="O44" t="n">
-        <v>559</v>
-      </c>
-      <c r="P44" t="n">
-        <v>536.4141414141416</v>
-      </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
